--- a/experiments/datasets/empirical_proof.xlsx
+++ b/experiments/datasets/empirical_proof.xlsx
@@ -60,7 +60,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -80,11 +80,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DEEAF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -137,9 +132,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7310,7 +7302,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Optimal found 0/100 times = 0.0%  (optimal utility ~9.1787)</t>
+          <t>Optimal found 69/100 times = 69.0%  (optimal utility ~9.1787)</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7338,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -7354,23 +7346,29 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="B6" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -7378,25 +7376,37 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>3.969</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="D7" s="4" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="B8" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -7404,12 +7414,18 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0</v>
+        <v>3.969</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -7417,24 +7433,30 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0</v>
+        <v>6.118</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="D10" s="4" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B11" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7465,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
+        <v>5.209</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -7456,7 +7478,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -7469,7 +7491,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
+        <v>3.969</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -7478,41 +7500,41 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B15" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B16" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B17" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7543,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0</v>
+        <v>6.118</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -7530,67 +7552,67 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B19" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B20" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B21" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B22" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B23" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7621,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -7608,28 +7630,28 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B25" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B26" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7660,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>0</v>
+        <v>6.118</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -7647,80 +7669,80 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B28" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B29" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B30" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B31" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B32" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B33" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7751,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -7738,28 +7760,28 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B35" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B36" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7790,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="4" t="n">
-        <v>0</v>
+        <v>5.209</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
@@ -7777,41 +7799,41 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B38" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B39" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B40" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7842,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="4" t="n">
-        <v>0</v>
+        <v>2.586</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
@@ -7829,15 +7851,15 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="n">
+      <c r="A42" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B42" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7868,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="4" t="n">
-        <v>0</v>
+        <v>6.118</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
@@ -7859,7 +7881,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -7872,7 +7894,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="4" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
@@ -7885,7 +7907,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>0</v>
+        <v>6.118</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -7894,15 +7916,15 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B47" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7933,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -7920,119 +7942,119 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B49" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="n">
+      <c r="A50" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B50" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B51" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n">
+      <c r="A52" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B52" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B53" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="n">
+      <c r="A54" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B54" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B55" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n">
+      <c r="A56" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B56" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B57" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8063,7 @@
         <v>54</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>0</v>
+        <v>3.969</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
@@ -8050,54 +8072,54 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B59" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="n">
+      <c r="A60" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B60" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B61" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n">
+      <c r="A62" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B62" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8128,7 @@
         <v>59</v>
       </c>
       <c r="B63" s="4" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
@@ -8115,15 +8137,15 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n">
+      <c r="A64" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B64" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8154,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="4" t="n">
-        <v>0</v>
+        <v>3.969</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
@@ -8145,7 +8167,7 @@
         <v>62</v>
       </c>
       <c r="B66" s="6" t="n">
-        <v>0</v>
+        <v>5.209</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
@@ -8158,7 +8180,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="4" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
@@ -8167,28 +8189,28 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="n">
+      <c r="A68" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B68" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B69" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8219,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="6" t="n">
-        <v>0</v>
+        <v>5.209</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
@@ -8206,41 +8228,41 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B71" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="n">
+      <c r="A72" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B72" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B73" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8271,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="6" t="n">
-        <v>0</v>
+        <v>3.969</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
@@ -8258,15 +8280,15 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B75" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8297,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="6" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
@@ -8284,54 +8306,54 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B77" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="n">
+      <c r="A78" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B78" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B79" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="n">
+      <c r="A80" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B80" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8362,7 @@
         <v>77</v>
       </c>
       <c r="B81" s="4" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
@@ -8349,106 +8371,106 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="n">
+      <c r="A82" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B82" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B83" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="n">
+      <c r="A84" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B84" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B85" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="n">
+      <c r="A86" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B86" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B87" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="n">
+      <c r="A88" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B88" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B89" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8479,7 @@
         <v>86</v>
       </c>
       <c r="B90" s="6" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
@@ -8466,106 +8488,106 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B91" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="n">
+      <c r="A92" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B92" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B93" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="n">
+      <c r="A94" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B94" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B95" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="n">
+      <c r="A96" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B96" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B97" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="n">
+      <c r="A98" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B98" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8596,7 @@
         <v>95</v>
       </c>
       <c r="B99" s="4" t="n">
-        <v>0</v>
+        <v>3.969</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
@@ -8583,15 +8605,15 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="n">
+      <c r="A100" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B100" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8622,7 @@
         <v>97</v>
       </c>
       <c r="B101" s="4" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
@@ -8609,15 +8631,15 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="6" t="n">
+      <c r="A102" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B102" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8648,7 @@
         <v>99</v>
       </c>
       <c r="B103" s="4" t="n">
-        <v>0</v>
+        <v>6.364</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
@@ -8635,15 +8657,15 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="n">
+      <c r="A104" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B104" s="5" t="n">
+        <v>9.179</v>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -10770,12 +10792,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0/100 optimal = 0%</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>69/100 optimal = 69%</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
